--- a/Calculo Nominas.xlsx
+++ b/Calculo Nominas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Comercial Minduval\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\proyecto-personal\paneladministrativo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16DCEEF5-906A-4D80-A922-570BBD7D3388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C57280A5-2086-4557-A45B-99CC5F590D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{D8044CBE-64B8-4F70-9BF0-4C45326A3771}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D8044CBE-64B8-4F70-9BF0-4C45326A3771}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabla" sheetId="3" r:id="rId1"/>
@@ -25,6 +25,17 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -328,7 +339,7 @@
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="#,##0_ ;\-#,##0\ "/>
+    <numFmt numFmtId="165" formatCode="#,##0_ ;\-#,##0\ "/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
@@ -792,7 +803,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="2" fillId="10" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="11" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -807,15 +818,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -825,33 +827,15 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="5" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -864,27 +848,18 @@
     <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="9" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -902,7 +877,7 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="41" fontId="7" fillId="12" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="7" fillId="12" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="12" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -917,33 +892,22 @@
     <xf numFmtId="41" fontId="3" fillId="13" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="13" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="13" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="11" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="11" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="11" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -956,12 +920,40 @@
     <xf numFmtId="164" fontId="5" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="12" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="12" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -972,34 +964,51 @@
     <xf numFmtId="0" fontId="8" fillId="12" borderId="0" xfId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="12" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="12" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="12" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="11" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="11" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="4" builtinId="8"/>
@@ -1141,9 +1150,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1181,7 +1190,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1287,7 +1296,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1429,7 +1438,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1457,812 +1466,810 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="11" t="s">
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="12" t="s">
+      <c r="G1" s="74"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="74"/>
+      <c r="J1" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="13" t="s">
+      <c r="K1" s="75"/>
+      <c r="L1" s="75"/>
+      <c r="M1" s="75"/>
+      <c r="N1" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="14" t="s">
+      <c r="O1" s="76"/>
+      <c r="P1" s="76"/>
+      <c r="Q1" s="76"/>
+      <c r="R1" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="S1" s="15" t="s">
+      <c r="S1" s="78" t="s">
         <v>5</v>
       </c>
-      <c r="T1" s="16" t="s">
+      <c r="T1" s="64" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="G2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="19" t="s">
+      <c r="I2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="J2" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="K2" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="21" t="s">
+      <c r="L2" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="21" t="s">
+      <c r="M2" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="N2" s="22" t="s">
+      <c r="N2" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="O2" s="23" t="s">
+      <c r="O2" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="P2" s="23" t="s">
+      <c r="P2" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="Q2" s="23" t="s">
+      <c r="Q2" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="R2" s="14"/>
-      <c r="S2" s="15"/>
-      <c r="T2" s="16"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="64"/>
       <c r="U2" s="6"/>
-      <c r="V2" s="37" t="s">
+      <c r="V2" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="W2" s="38" t="s">
+      <c r="W2" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="X2" s="37" t="s">
+      <c r="X2" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="Y2" s="37"/>
-      <c r="Z2" s="37" t="s">
+      <c r="Y2" s="25"/>
+      <c r="Z2" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="AA2" s="38" t="s">
+      <c r="AA2" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="AB2" s="37" t="s">
+      <c r="AB2" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="AC2" s="37" t="s">
+      <c r="AC2" s="25" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="B3" s="25">
+      <c r="B3" s="16">
         <v>2000000</v>
       </c>
-      <c r="C3" s="25">
+      <c r="C3" s="16">
         <v>164000</v>
       </c>
-      <c r="D3" s="25">
+      <c r="D3" s="16">
         <v>1000000</v>
       </c>
-      <c r="E3" s="25">
+      <c r="E3" s="16">
         <f t="shared" ref="E3" si="0">+SUM(B3:D3)</f>
         <v>3164000</v>
       </c>
-      <c r="F3" s="25">
+      <c r="F3" s="16">
         <f>+(E3-D3)*8.33%</f>
         <v>180261.2</v>
       </c>
-      <c r="G3" s="25">
+      <c r="G3" s="16">
         <f>+F3*12%</f>
         <v>21631.344000000001</v>
       </c>
-      <c r="H3" s="25">
+      <c r="H3" s="16">
         <f>+(E3-D3)*8.33%</f>
         <v>180261.2</v>
       </c>
-      <c r="I3" s="25">
+      <c r="I3" s="16">
         <f>+B3*4.16%</f>
         <v>83200</v>
       </c>
-      <c r="J3" s="25">
+      <c r="J3" s="16">
         <f>+B3*6.96%</f>
         <v>139200</v>
       </c>
-      <c r="K3" s="25">
+      <c r="K3" s="16">
         <f>+B3*4%</f>
         <v>80000</v>
       </c>
-      <c r="L3" s="25">
+      <c r="L3" s="16">
         <f>+B3*12%</f>
         <v>240000</v>
       </c>
-      <c r="M3" s="25">
+      <c r="M3" s="16">
         <f>+B3*4%</f>
         <v>80000</v>
       </c>
-      <c r="N3" s="25">
-        <f>+$N$12*26</f>
-        <v>520000</v>
-      </c>
-      <c r="O3" s="25">
-        <f>+$O$12*26</f>
-        <v>481000</v>
-      </c>
-      <c r="P3" s="25">
+      <c r="N3" s="16">
+        <v>0</v>
+      </c>
+      <c r="O3" s="16">
+        <v>0</v>
+      </c>
+      <c r="P3" s="16">
         <f>+$X$13</f>
         <v>263900</v>
       </c>
-      <c r="Q3" s="25">
-        <f>+$AB$13</f>
+      <c r="Q3" s="16">
+        <f t="shared" ref="Q3:Q9" si="1">+$AB$13</f>
         <v>115000</v>
       </c>
-      <c r="R3" s="26">
+      <c r="R3" s="17">
         <f>+SUM(E3:Q3)</f>
-        <v>5548453.7440000009</v>
-      </c>
-      <c r="S3" s="25">
+        <v>4547453.7440000009</v>
+      </c>
+      <c r="S3" s="16">
         <f>+R3/26</f>
-        <v>213402.06707692312</v>
-      </c>
-      <c r="T3" s="25">
+        <v>174902.06707692312</v>
+      </c>
+      <c r="T3" s="16">
         <f>+S3/8</f>
-        <v>26675.25838461539</v>
+        <v>21862.75838461539</v>
       </c>
       <c r="U3" s="3"/>
-      <c r="V3" s="39" t="s">
+      <c r="V3" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="W3" s="40">
+      <c r="W3" s="28">
         <v>128000</v>
       </c>
-      <c r="X3" s="40">
+      <c r="X3" s="28">
         <v>128000</v>
       </c>
-      <c r="Y3" s="39"/>
-      <c r="Z3" s="39" t="s">
+      <c r="Y3" s="27"/>
+      <c r="Z3" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="AA3" s="41">
+      <c r="AA3" s="29">
         <v>20000</v>
       </c>
-      <c r="AB3" s="41">
+      <c r="AB3" s="29">
         <v>20000</v>
       </c>
-      <c r="AC3" s="36"/>
+      <c r="AC3" s="24"/>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="25">
+      <c r="B4" s="16">
         <v>2000000</v>
       </c>
-      <c r="C4" s="25">
+      <c r="C4" s="16">
         <v>164000</v>
       </c>
-      <c r="D4" s="25">
+      <c r="D4" s="16">
         <v>700000</v>
       </c>
-      <c r="E4" s="25">
+      <c r="E4" s="16">
         <f>+SUM(B4:D4)</f>
         <v>2864000</v>
       </c>
-      <c r="F4" s="25">
+      <c r="F4" s="16">
         <f>+(E4-D4)*8.33%</f>
         <v>180261.2</v>
       </c>
-      <c r="G4" s="25">
+      <c r="G4" s="16">
         <f>+F4*12%</f>
         <v>21631.344000000001</v>
       </c>
-      <c r="H4" s="25">
+      <c r="H4" s="16">
         <f>+(E4-D4)*8.33%</f>
         <v>180261.2</v>
       </c>
-      <c r="I4" s="25">
+      <c r="I4" s="16">
         <f>+B4*4.16%</f>
         <v>83200</v>
       </c>
-      <c r="J4" s="25">
+      <c r="J4" s="16">
         <f>+B4*6.96%</f>
         <v>139200</v>
       </c>
-      <c r="K4" s="25">
+      <c r="K4" s="16">
         <f>+B4*4%</f>
         <v>80000</v>
       </c>
-      <c r="L4" s="25">
+      <c r="L4" s="16">
         <f>+B4*12%</f>
         <v>240000</v>
       </c>
-      <c r="M4" s="25">
+      <c r="M4" s="16">
         <f>+B4*4%</f>
         <v>80000</v>
       </c>
-      <c r="N4" s="25">
-        <f t="shared" ref="N4:N9" si="1">+$N$12*26</f>
+      <c r="N4" s="16">
+        <f t="shared" ref="N4:N9" si="2">+$N$12*26</f>
         <v>520000</v>
       </c>
-      <c r="O4" s="25">
-        <f t="shared" ref="O4:O9" si="2">+$O$12*26</f>
+      <c r="O4" s="16">
+        <f t="shared" ref="O4:O9" si="3">+$O$12*26</f>
         <v>481000</v>
       </c>
-      <c r="P4" s="25">
+      <c r="P4" s="16">
         <f>+$X$13</f>
         <v>263900</v>
       </c>
-      <c r="Q4" s="25">
-        <f>+$AB$13</f>
+      <c r="Q4" s="16">
+        <f t="shared" si="1"/>
         <v>115000</v>
       </c>
-      <c r="R4" s="26">
+      <c r="R4" s="17">
         <f>+SUM(E4:Q4)</f>
         <v>5248453.7440000009</v>
       </c>
-      <c r="S4" s="25">
+      <c r="S4" s="16">
         <f>+R4/26</f>
         <v>201863.60553846156</v>
       </c>
-      <c r="T4" s="25">
+      <c r="T4" s="16">
         <f>+S4/8</f>
         <v>25232.950692307695</v>
       </c>
       <c r="U4" s="3"/>
-      <c r="V4" s="39" t="s">
+      <c r="V4" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="W4" s="40">
+      <c r="W4" s="28">
         <f>31500*2</f>
         <v>63000</v>
       </c>
-      <c r="X4" s="40">
+      <c r="X4" s="28">
         <f>30000*2</f>
         <v>60000</v>
       </c>
-      <c r="Y4" s="39"/>
-      <c r="Z4" s="39" t="s">
+      <c r="Y4" s="27"/>
+      <c r="Z4" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="AA4" s="41">
+      <c r="AA4" s="29">
         <v>16000</v>
       </c>
-      <c r="AB4" s="41">
+      <c r="AB4" s="29">
         <v>16000</v>
       </c>
-      <c r="AC4" s="36"/>
+      <c r="AC4" s="24"/>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="B5" s="25">
+      <c r="B5" s="16">
         <v>2000000</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="16">
         <v>164000</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="16">
         <v>1000000</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="16">
         <f>+SUM(B5:D5)</f>
         <v>3164000</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="16">
         <f>+(E5-D5)*8.33%</f>
         <v>180261.2</v>
       </c>
-      <c r="G5" s="25">
+      <c r="G5" s="16">
         <f>+F5*12%</f>
         <v>21631.344000000001</v>
       </c>
-      <c r="H5" s="25">
+      <c r="H5" s="16">
         <f>+(E5-D5)*8.33%</f>
         <v>180261.2</v>
       </c>
-      <c r="I5" s="25">
+      <c r="I5" s="16">
         <f>+B5*4.16%</f>
         <v>83200</v>
       </c>
-      <c r="J5" s="25">
+      <c r="J5" s="16">
         <f>+B5*6.96%</f>
         <v>139200</v>
       </c>
-      <c r="K5" s="25">
+      <c r="K5" s="16">
         <f>+B5*4%</f>
         <v>80000</v>
       </c>
-      <c r="L5" s="25">
+      <c r="L5" s="16">
         <f>+B5*12%</f>
         <v>240000</v>
       </c>
-      <c r="M5" s="25">
+      <c r="M5" s="16">
         <f>+B5*4%</f>
         <v>80000</v>
       </c>
-      <c r="N5" s="25">
-        <f t="shared" si="1"/>
+      <c r="N5" s="16">
+        <f t="shared" si="2"/>
         <v>520000</v>
       </c>
-      <c r="O5" s="25">
-        <f t="shared" si="2"/>
+      <c r="O5" s="16">
+        <f t="shared" si="3"/>
         <v>481000</v>
       </c>
-      <c r="P5" s="25">
+      <c r="P5" s="16">
         <f>+$W$13</f>
         <v>425600</v>
       </c>
-      <c r="Q5" s="25">
-        <f>+$AB$13</f>
+      <c r="Q5" s="16">
+        <f t="shared" si="1"/>
         <v>115000</v>
       </c>
-      <c r="R5" s="26">
+      <c r="R5" s="17">
         <f>+SUM(E5:Q5)</f>
         <v>5710153.7440000009</v>
       </c>
-      <c r="S5" s="25">
+      <c r="S5" s="16">
         <f>+R5/26</f>
         <v>219621.29784615387</v>
       </c>
-      <c r="T5" s="25">
+      <c r="T5" s="16">
         <f>+S5/8</f>
         <v>27452.662230769234</v>
       </c>
       <c r="U5" s="3"/>
-      <c r="V5" s="39" t="s">
+      <c r="V5" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="W5" s="40">
+      <c r="W5" s="28">
         <f>45000*2</f>
         <v>90000</v>
       </c>
-      <c r="X5" s="40">
+      <c r="X5" s="28">
         <f>35000*2</f>
         <v>70000</v>
       </c>
-      <c r="Y5" s="39"/>
-      <c r="Z5" s="39" t="s">
+      <c r="Y5" s="27"/>
+      <c r="Z5" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="AA5" s="41">
+      <c r="AA5" s="29">
         <v>16000</v>
       </c>
-      <c r="AB5" s="41">
+      <c r="AB5" s="29">
         <v>16000</v>
       </c>
-      <c r="AC5" s="36"/>
+      <c r="AC5" s="24"/>
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="B6" s="25">
+      <c r="B6" s="16">
         <v>2000000</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="16">
         <v>164000</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="16">
         <v>800000</v>
       </c>
-      <c r="E6" s="25">
-        <f t="shared" ref="E6" si="3">+SUM(B6:D6)</f>
+      <c r="E6" s="16">
+        <f t="shared" ref="E6" si="4">+SUM(B6:D6)</f>
         <v>2964000</v>
       </c>
-      <c r="F6" s="25">
-        <f t="shared" ref="F6" si="4">+(E6-D6)*8.33%</f>
+      <c r="F6" s="16">
+        <f t="shared" ref="F6" si="5">+(E6-D6)*8.33%</f>
         <v>180261.2</v>
       </c>
-      <c r="G6" s="25">
-        <f t="shared" ref="G6" si="5">+F6*12%</f>
+      <c r="G6" s="16">
+        <f t="shared" ref="G6" si="6">+F6*12%</f>
         <v>21631.344000000001</v>
       </c>
-      <c r="H6" s="25">
-        <f t="shared" ref="H6" si="6">+(E6-D6)*8.33%</f>
+      <c r="H6" s="16">
+        <f t="shared" ref="H6" si="7">+(E6-D6)*8.33%</f>
         <v>180261.2</v>
       </c>
-      <c r="I6" s="25">
-        <f t="shared" ref="I6" si="7">+B6*4.16%</f>
+      <c r="I6" s="16">
+        <f t="shared" ref="I6" si="8">+B6*4.16%</f>
         <v>83200</v>
       </c>
-      <c r="J6" s="25">
-        <f t="shared" ref="J6" si="8">+B6*6.96%</f>
+      <c r="J6" s="16">
+        <f t="shared" ref="J6" si="9">+B6*6.96%</f>
         <v>139200</v>
       </c>
-      <c r="K6" s="25">
-        <f t="shared" ref="K6" si="9">+B6*4%</f>
+      <c r="K6" s="16">
+        <f t="shared" ref="K6" si="10">+B6*4%</f>
         <v>80000</v>
       </c>
-      <c r="L6" s="25">
-        <f t="shared" ref="L6" si="10">+B6*12%</f>
+      <c r="L6" s="16">
+        <f t="shared" ref="L6" si="11">+B6*12%</f>
         <v>240000</v>
       </c>
-      <c r="M6" s="25">
-        <f t="shared" ref="M6" si="11">+B6*4%</f>
+      <c r="M6" s="16">
+        <f t="shared" ref="M6" si="12">+B6*4%</f>
         <v>80000</v>
       </c>
-      <c r="N6" s="25">
-        <f t="shared" si="1"/>
+      <c r="N6" s="16">
+        <f t="shared" si="2"/>
         <v>520000</v>
       </c>
-      <c r="O6" s="25">
-        <f t="shared" si="2"/>
+      <c r="O6" s="16">
+        <f t="shared" si="3"/>
         <v>481000</v>
       </c>
-      <c r="P6" s="25">
+      <c r="P6" s="16">
         <f>+$W$13</f>
         <v>425600</v>
       </c>
-      <c r="Q6" s="25">
-        <f>+$AB$13</f>
+      <c r="Q6" s="16">
+        <f t="shared" si="1"/>
         <v>115000</v>
       </c>
-      <c r="R6" s="26">
-        <f t="shared" ref="R6" si="12">+SUM(E6:Q6)</f>
+      <c r="R6" s="17">
+        <f t="shared" ref="R6" si="13">+SUM(E6:Q6)</f>
         <v>5510153.7440000009</v>
       </c>
-      <c r="S6" s="25">
-        <f t="shared" ref="S6" si="13">+R6/26</f>
+      <c r="S6" s="16">
+        <f t="shared" ref="S6" si="14">+R6/26</f>
         <v>211928.99015384619</v>
       </c>
-      <c r="T6" s="25">
-        <f t="shared" ref="T6" si="14">+S6/8</f>
+      <c r="T6" s="16">
+        <f t="shared" ref="T6" si="15">+S6/8</f>
         <v>26491.123769230773</v>
       </c>
       <c r="U6" s="3"/>
-      <c r="V6" s="39" t="s">
+      <c r="V6" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="W6" s="40">
+      <c r="W6" s="28">
         <v>43600</v>
       </c>
-      <c r="X6" s="40"/>
-      <c r="Y6" s="39"/>
-      <c r="Z6" s="39" t="s">
+      <c r="X6" s="28"/>
+      <c r="Y6" s="27"/>
+      <c r="Z6" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="AA6" s="41">
+      <c r="AA6" s="29">
         <v>65000</v>
       </c>
-      <c r="AB6" s="41">
+      <c r="AB6" s="29">
         <v>0</v>
       </c>
-      <c r="AC6" s="36"/>
+      <c r="AC6" s="24"/>
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="16">
         <v>1700000</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="16">
         <v>164000</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="16">
         <v>300000</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="16">
         <f>+SUM(B7:D7)</f>
         <v>2164000</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="16">
         <f>+(E7-D7)*8.33%</f>
         <v>155271.20000000001</v>
       </c>
-      <c r="G7" s="25">
+      <c r="G7" s="16">
         <f>+F7*12%</f>
         <v>18632.544000000002</v>
       </c>
-      <c r="H7" s="25">
+      <c r="H7" s="16">
         <f>+(E7-D7)*8.33%</f>
         <v>155271.20000000001</v>
       </c>
-      <c r="I7" s="25">
+      <c r="I7" s="16">
         <f>+B7*4.16%</f>
         <v>70720</v>
       </c>
-      <c r="J7" s="25">
+      <c r="J7" s="16">
         <f>+B7*6.96%</f>
         <v>118319.99999999999</v>
       </c>
-      <c r="K7" s="25">
+      <c r="K7" s="16">
         <f>+B7*4%</f>
         <v>68000</v>
       </c>
-      <c r="L7" s="25">
+      <c r="L7" s="16">
         <f>+B7*12%</f>
         <v>204000</v>
       </c>
-      <c r="M7" s="25">
+      <c r="M7" s="16">
         <f>+B7*4%</f>
         <v>68000</v>
       </c>
-      <c r="N7" s="25">
-        <f t="shared" si="1"/>
+      <c r="N7" s="16">
+        <f t="shared" si="2"/>
         <v>520000</v>
       </c>
-      <c r="O7" s="25">
-        <f t="shared" si="2"/>
+      <c r="O7" s="16">
+        <f t="shared" si="3"/>
         <v>481000</v>
       </c>
-      <c r="P7" s="25">
+      <c r="P7" s="16">
         <f>+$W$13</f>
         <v>425600</v>
       </c>
-      <c r="Q7" s="25">
-        <f>+$AB$13</f>
+      <c r="Q7" s="16">
+        <f t="shared" si="1"/>
         <v>115000</v>
       </c>
-      <c r="R7" s="26">
+      <c r="R7" s="17">
         <f>+SUM(E7:Q7)</f>
         <v>4563814.9440000001</v>
       </c>
-      <c r="S7" s="25">
+      <c r="S7" s="16">
         <f>+R7/26</f>
         <v>175531.34400000001</v>
       </c>
-      <c r="T7" s="25">
+      <c r="T7" s="16">
         <f>+S7/8</f>
         <v>21941.418000000001</v>
       </c>
       <c r="U7" s="3"/>
-      <c r="V7" s="39" t="s">
+      <c r="V7" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="W7" s="40">
+      <c r="W7" s="28">
         <f>35800*2</f>
         <v>71600</v>
       </c>
-      <c r="X7" s="40"/>
-      <c r="Y7" s="39"/>
-      <c r="Z7" s="39" t="s">
+      <c r="X7" s="28"/>
+      <c r="Y7" s="27"/>
+      <c r="Z7" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="AA7" s="41">
+      <c r="AA7" s="29">
         <v>35000</v>
       </c>
-      <c r="AB7" s="41">
+      <c r="AB7" s="29">
         <v>35000</v>
       </c>
-      <c r="AC7" s="36"/>
+      <c r="AC7" s="24"/>
     </row>
     <row r="8" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="16">
         <v>1300000</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="16">
         <v>164000</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="16">
         <v>200000</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="16">
         <f>+SUM(B8:D8)</f>
         <v>1664000</v>
       </c>
-      <c r="F8" s="25">
-        <f t="shared" ref="F8:F9" si="15">+(E8-D8)*8.33%</f>
+      <c r="F8" s="16">
+        <f t="shared" ref="F8:F9" si="16">+(E8-D8)*8.33%</f>
         <v>121951.2</v>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="16">
         <f>+F8*12%</f>
         <v>14634.143999999998</v>
       </c>
-      <c r="H8" s="25">
-        <f t="shared" ref="H8:H9" si="16">+(E8-D8)*8.33%</f>
+      <c r="H8" s="16">
+        <f t="shared" ref="H8:H9" si="17">+(E8-D8)*8.33%</f>
         <v>121951.2</v>
       </c>
-      <c r="I8" s="25">
-        <f t="shared" ref="I8:I9" si="17">+B8*4.16%</f>
+      <c r="I8" s="16">
+        <f t="shared" ref="I8:I9" si="18">+B8*4.16%</f>
         <v>54080</v>
       </c>
-      <c r="J8" s="25">
-        <f t="shared" ref="J8:J9" si="18">+B8*6.96%</f>
+      <c r="J8" s="16">
+        <f t="shared" ref="J8:J9" si="19">+B8*6.96%</f>
         <v>90480</v>
       </c>
-      <c r="K8" s="25">
+      <c r="K8" s="16">
         <f>+B8*4%</f>
         <v>52000</v>
       </c>
-      <c r="L8" s="25">
+      <c r="L8" s="16">
         <f>+B8*12%</f>
         <v>156000</v>
       </c>
-      <c r="M8" s="25">
+      <c r="M8" s="16">
         <f>+B8*4%</f>
         <v>52000</v>
       </c>
-      <c r="N8" s="25">
-        <f t="shared" si="1"/>
+      <c r="N8" s="16">
+        <f t="shared" si="2"/>
         <v>520000</v>
       </c>
-      <c r="O8" s="25">
-        <f t="shared" si="2"/>
+      <c r="O8" s="16">
+        <f t="shared" si="3"/>
         <v>481000</v>
       </c>
-      <c r="P8" s="25">
+      <c r="P8" s="16">
         <f>+$W$13</f>
         <v>425600</v>
       </c>
-      <c r="Q8" s="25">
-        <f>+$AB$13</f>
+      <c r="Q8" s="16">
+        <f t="shared" si="1"/>
         <v>115000</v>
       </c>
-      <c r="R8" s="26">
+      <c r="R8" s="17">
         <f>+SUM(E8:Q8)</f>
         <v>3868696.5439999998</v>
       </c>
-      <c r="S8" s="25">
+      <c r="S8" s="16">
         <f>+R8/26</f>
         <v>148796.02092307693</v>
       </c>
-      <c r="T8" s="25">
+      <c r="T8" s="16">
         <f>+S8/8</f>
         <v>18599.502615384616</v>
       </c>
       <c r="U8" s="3"/>
-      <c r="V8" s="39" t="s">
+      <c r="V8" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="W8" s="40">
+      <c r="W8" s="28">
         <v>11500</v>
       </c>
-      <c r="X8" s="40"/>
-      <c r="Y8" s="39"/>
-      <c r="Z8" s="39" t="s">
+      <c r="X8" s="28"/>
+      <c r="Y8" s="27"/>
+      <c r="Z8" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="AA8" s="41">
+      <c r="AA8" s="29">
         <v>8000</v>
       </c>
-      <c r="AB8" s="41">
+      <c r="AB8" s="29">
         <v>8000</v>
       </c>
-      <c r="AC8" s="36"/>
+      <c r="AC8" s="24"/>
     </row>
     <row r="9" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="24" t="s">
+      <c r="A9" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="16">
         <v>1700000</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="16">
         <v>164000</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="16">
         <v>300000</v>
       </c>
-      <c r="E9" s="25">
-        <f t="shared" ref="E9" si="19">+SUM(B9:D9)</f>
+      <c r="E9" s="16">
+        <f t="shared" ref="E9" si="20">+SUM(B9:D9)</f>
         <v>2164000</v>
       </c>
-      <c r="F9" s="25">
-        <f t="shared" si="15"/>
-        <v>155271.20000000001</v>
-      </c>
-      <c r="G9" s="25">
-        <f t="shared" ref="G9" si="20">+F9*12%</f>
-        <v>18632.544000000002</v>
-      </c>
-      <c r="H9" s="25">
+      <c r="F9" s="16">
         <f t="shared" si="16"/>
         <v>155271.20000000001</v>
       </c>
-      <c r="I9" s="25">
+      <c r="G9" s="16">
+        <f t="shared" ref="G9" si="21">+F9*12%</f>
+        <v>18632.544000000002</v>
+      </c>
+      <c r="H9" s="16">
         <f t="shared" si="17"/>
+        <v>155271.20000000001</v>
+      </c>
+      <c r="I9" s="16">
+        <f t="shared" si="18"/>
         <v>70720</v>
       </c>
-      <c r="J9" s="25">
-        <f t="shared" si="18"/>
+      <c r="J9" s="16">
+        <f t="shared" si="19"/>
         <v>118319.99999999999</v>
       </c>
-      <c r="K9" s="25">
-        <f t="shared" ref="K9" si="21">+B9*4%</f>
+      <c r="K9" s="16">
+        <f t="shared" ref="K9" si="22">+B9*4%</f>
         <v>68000</v>
       </c>
-      <c r="L9" s="25">
-        <f t="shared" ref="L9" si="22">+B9*12%</f>
+      <c r="L9" s="16">
+        <f t="shared" ref="L9" si="23">+B9*12%</f>
         <v>204000</v>
       </c>
-      <c r="M9" s="25">
-        <f t="shared" ref="M9" si="23">+B9*4%</f>
+      <c r="M9" s="16">
+        <f t="shared" ref="M9" si="24">+B9*4%</f>
         <v>68000</v>
       </c>
-      <c r="N9" s="25">
-        <f t="shared" si="1"/>
+      <c r="N9" s="16">
+        <f t="shared" si="2"/>
         <v>520000</v>
       </c>
-      <c r="O9" s="25">
-        <f t="shared" si="2"/>
+      <c r="O9" s="16">
+        <f t="shared" si="3"/>
         <v>481000</v>
       </c>
-      <c r="P9" s="25">
+      <c r="P9" s="16">
         <f>+$W$13</f>
         <v>425600</v>
       </c>
-      <c r="Q9" s="25">
-        <f>+$AB$13</f>
+      <c r="Q9" s="16">
+        <f t="shared" si="1"/>
         <v>115000</v>
       </c>
-      <c r="R9" s="26">
-        <f t="shared" ref="R9" si="24">+SUM(E9:Q9)</f>
+      <c r="R9" s="17">
+        <f t="shared" ref="R9" si="25">+SUM(E9:Q9)</f>
         <v>4563814.9440000001</v>
       </c>
-      <c r="S9" s="25">
-        <f t="shared" ref="S9" si="25">+R9/26</f>
+      <c r="S9" s="16">
+        <f t="shared" ref="S9" si="26">+R9/26</f>
         <v>175531.34400000001</v>
       </c>
-      <c r="T9" s="25">
-        <f t="shared" ref="T9" si="26">+S9/8</f>
+      <c r="T9" s="16">
+        <f t="shared" ref="T9" si="27">+S9/8</f>
         <v>21941.418000000001</v>
       </c>
       <c r="U9" s="3"/>
-      <c r="V9" s="39" t="s">
+      <c r="V9" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="W9" s="40">
+      <c r="W9" s="28">
         <v>4500</v>
       </c>
-      <c r="X9" s="40">
+      <c r="X9" s="28">
         <v>4500</v>
       </c>
-      <c r="Y9" s="39"/>
-      <c r="Z9" s="39" t="s">
+      <c r="Y9" s="27"/>
+      <c r="Z9" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="AA9" s="41">
+      <c r="AA9" s="29">
         <f>IF(AC9="SI",80000,0)</f>
         <v>80000</v>
       </c>
-      <c r="AB9" s="41">
+      <c r="AB9" s="29">
         <v>0</v>
       </c>
-      <c r="AC9" s="42" t="s">
+      <c r="AC9" s="30" t="s">
         <v>61</v>
       </c>
     </row>
@@ -2277,33 +2284,33 @@
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="U10" s="3"/>
-      <c r="V10" s="39" t="s">
+      <c r="V10" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="W10" s="40">
+      <c r="W10" s="28">
         <v>1400</v>
       </c>
-      <c r="X10" s="40">
+      <c r="X10" s="28">
         <v>1400</v>
       </c>
-      <c r="Y10" s="39"/>
-      <c r="Z10" s="39" t="s">
+      <c r="Y10" s="27"/>
+      <c r="Z10" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="AA10" s="41">
+      <c r="AA10" s="29">
         <v>20000</v>
       </c>
-      <c r="AB10" s="41">
+      <c r="AB10" s="29">
         <v>20000</v>
       </c>
-      <c r="AC10" s="36"/>
+      <c r="AC10" s="24"/>
     </row>
     <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B11" s="1">
-        <v>0.315</v>
+        <v>0</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
@@ -2312,24 +2319,24 @@
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
-      <c r="M11" s="27" t="s">
+      <c r="M11" s="68" t="s">
         <v>57</v>
       </c>
-      <c r="N11" s="28"/>
-      <c r="O11" s="29"/>
+      <c r="N11" s="18"/>
+      <c r="O11" s="19"/>
       <c r="U11" s="3"/>
-      <c r="V11" s="39" t="s">
+      <c r="V11" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="W11" s="40">
+      <c r="W11" s="28">
         <v>12000</v>
       </c>
-      <c r="X11" s="39"/>
-      <c r="Y11" s="39"/>
-      <c r="Z11" s="39"/>
-      <c r="AA11" s="41"/>
-      <c r="AB11" s="41"/>
-      <c r="AC11" s="36"/>
+      <c r="X11" s="27"/>
+      <c r="Y11" s="27"/>
+      <c r="Z11" s="27"/>
+      <c r="AA11" s="29"/>
+      <c r="AB11" s="29"/>
+      <c r="AC11" s="24"/>
     </row>
     <row r="12" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
@@ -2341,22 +2348,22 @@
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
-      <c r="M12" s="30"/>
-      <c r="N12" s="31">
+      <c r="M12" s="69"/>
+      <c r="N12" s="20">
         <v>20000</v>
       </c>
-      <c r="O12" s="32">
+      <c r="O12" s="21">
         <v>18500</v>
       </c>
       <c r="U12" s="3"/>
-      <c r="V12" s="39"/>
-      <c r="W12" s="40"/>
-      <c r="X12" s="39"/>
-      <c r="Y12" s="39"/>
-      <c r="Z12" s="39"/>
-      <c r="AA12" s="41"/>
-      <c r="AB12" s="41"/>
-      <c r="AC12" s="36"/>
+      <c r="V12" s="27"/>
+      <c r="W12" s="28"/>
+      <c r="X12" s="27"/>
+      <c r="Y12" s="27"/>
+      <c r="Z12" s="27"/>
+      <c r="AA12" s="29"/>
+      <c r="AB12" s="29"/>
+      <c r="AC12" s="24"/>
     </row>
     <row r="13" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
@@ -2368,59 +2375,59 @@
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
-      <c r="M13" s="33"/>
-      <c r="N13" s="34" t="s">
+      <c r="M13" s="70"/>
+      <c r="N13" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="O13" s="35" t="s">
+      <c r="O13" s="23" t="s">
         <v>20</v>
       </c>
       <c r="U13" s="3"/>
-      <c r="V13" s="43" t="s">
+      <c r="V13" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="W13" s="44">
+      <c r="W13" s="32">
         <f>SUM(W3:W12)</f>
         <v>425600</v>
       </c>
-      <c r="X13" s="45">
+      <c r="X13" s="33">
         <f>SUM(X3:X12)</f>
         <v>263900</v>
       </c>
-      <c r="Y13" s="39"/>
-      <c r="Z13" s="43" t="s">
+      <c r="Y13" s="27"/>
+      <c r="Z13" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="AA13" s="46">
+      <c r="AA13" s="34">
         <f>SUM(AA3:AA12)</f>
         <v>260000</v>
       </c>
-      <c r="AB13" s="46">
+      <c r="AB13" s="34">
         <f>SUM(AB3:AB12)</f>
         <v>115000</v>
       </c>
-      <c r="AC13" s="36"/>
+      <c r="AC13" s="24"/>
     </row>
     <row r="14" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A14" s="47" t="s">
+      <c r="A14" s="65" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="47"/>
-      <c r="C14" s="47"/>
-      <c r="D14" s="47"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="47"/>
-      <c r="G14" s="47"/>
-      <c r="H14" s="47"/>
-      <c r="I14" s="48" t="s">
+      <c r="B14" s="65"/>
+      <c r="C14" s="65"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="65"/>
+      <c r="G14" s="65"/>
+      <c r="H14" s="65"/>
+      <c r="I14" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="M14" s="36"/>
-      <c r="N14" s="36"/>
-      <c r="O14" s="36"/>
-    </row>
-    <row r="15" spans="1:29" ht="36" x14ac:dyDescent="0.25">
-      <c r="A15" s="49" t="s">
+      <c r="M14" s="24"/>
+      <c r="N14" s="24"/>
+      <c r="O14" s="24"/>
+    </row>
+    <row r="15" spans="1:29" ht="48" x14ac:dyDescent="0.25">
+      <c r="A15" s="35" t="s">
         <v>7</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -2444,265 +2451,265 @@
       <c r="H15" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="I15" s="50"/>
+      <c r="I15" s="67"/>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A16" s="51" t="s">
+      <c r="A16" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="B16" s="52">
+      <c r="B16" s="37">
         <f>+(($T$3*1)/(1-$B$11))</f>
-        <v>38941.98304323414</v>
-      </c>
-      <c r="C16" s="52">
+        <v>21862.75838461539</v>
+      </c>
+      <c r="C16" s="37">
         <f>+(($T$3*0.35)/(1-$B$11))</f>
-        <v>13629.694065131949</v>
-      </c>
-      <c r="D16" s="52">
+        <v>7651.9654346153857</v>
+      </c>
+      <c r="D16" s="37">
         <f>+(($T$3*1.25)/(1-$B$11))</f>
-        <v>48677.478804042687</v>
-      </c>
-      <c r="E16" s="52">
+        <v>27328.447980769237</v>
+      </c>
+      <c r="E16" s="37">
         <f>+(($T$3*1.75)/(1-$B$11))</f>
-        <v>68148.470325659757</v>
-      </c>
-      <c r="F16" s="52">
+        <v>38259.827173076934</v>
+      </c>
+      <c r="F16" s="37">
         <f>+(($T$3*1.75)/(1-$B$11))</f>
-        <v>68148.470325659757</v>
-      </c>
-      <c r="G16" s="52">
+        <v>38259.827173076934</v>
+      </c>
+      <c r="G16" s="37">
         <f>+(($T$3*2)/(1-$B$11))</f>
-        <v>77883.966086468281</v>
-      </c>
-      <c r="H16" s="52">
+        <v>43725.51676923078</v>
+      </c>
+      <c r="H16" s="37">
         <f>+(($T$3*2.5)/(1-$B$11))</f>
-        <v>97354.957608085373</v>
-      </c>
-      <c r="I16" s="52">
+        <v>54656.895961538474</v>
+      </c>
+      <c r="I16" s="37">
         <f>+B16*8</f>
-        <v>311535.86434587312</v>
+        <v>174902.06707692312</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A17" s="51" t="s">
+      <c r="A17" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="52">
+      <c r="B17" s="37">
         <f>+(($T$4*1)/(1-$B$11))</f>
-        <v>36836.424368332402</v>
-      </c>
-      <c r="C17" s="52">
+        <v>25232.950692307695</v>
+      </c>
+      <c r="C17" s="37">
         <f>+(($T$4*0.35)/(1-$B$11))</f>
-        <v>12892.748528916338</v>
-      </c>
-      <c r="D17" s="52">
+        <v>8831.5327423076924</v>
+      </c>
+      <c r="D17" s="37">
         <f>+(($T$4*1.25)/(1-$B$11))</f>
-        <v>46045.530460415503</v>
-      </c>
-      <c r="E17" s="52">
+        <v>31541.18836538462</v>
+      </c>
+      <c r="E17" s="37">
         <f>+(($T$4*1.75)/(1-$B$11))</f>
-        <v>64463.742644581696</v>
-      </c>
-      <c r="F17" s="52">
+        <v>44157.663711538466</v>
+      </c>
+      <c r="F17" s="37">
         <f>+(($T$4*1.75)/(1-$B$11))</f>
-        <v>64463.742644581696</v>
-      </c>
-      <c r="G17" s="52">
+        <v>44157.663711538466</v>
+      </c>
+      <c r="G17" s="37">
         <f>+(($T$4*2)/(1-$B$11))</f>
-        <v>73672.848736664804</v>
-      </c>
-      <c r="H17" s="52">
+        <v>50465.90138461539</v>
+      </c>
+      <c r="H17" s="37">
         <f>+(($T$4*2.5)/(1-$B$11))</f>
-        <v>92091.060920831005</v>
-      </c>
-      <c r="I17" s="52">
-        <f t="shared" ref="I17:I22" si="27">+B17*8</f>
-        <v>294691.39494665922</v>
+        <v>63082.37673076924</v>
+      </c>
+      <c r="I17" s="37">
+        <f t="shared" ref="I17:I22" si="28">+B17*8</f>
+        <v>201863.60553846156</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A18" s="24" t="s">
+      <c r="A18" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="B18" s="52">
+      <c r="B18" s="37">
         <f>+(($T$5*1)/(1-$B$11))</f>
-        <v>40076.879169006177</v>
-      </c>
-      <c r="C18" s="52">
+        <v>27452.662230769234</v>
+      </c>
+      <c r="C18" s="37">
         <f>+(($T$5*0.35)/(1-$B$11))</f>
-        <v>14026.907709152161</v>
-      </c>
-      <c r="D18" s="52">
+        <v>9608.4317807692314</v>
+      </c>
+      <c r="D18" s="37">
         <f>+(($T$5*1.25)/(1-$B$11))</f>
-        <v>50096.098961257725</v>
-      </c>
-      <c r="E18" s="52">
+        <v>34315.827788461545</v>
+      </c>
+      <c r="E18" s="37">
         <f>+(($T$5*1.75)/(1-$B$11))</f>
-        <v>70134.538545760806</v>
-      </c>
-      <c r="F18" s="52">
+        <v>48042.158903846161</v>
+      </c>
+      <c r="F18" s="37">
         <f>+(($T$5*1.75)/(1-$B$11))</f>
-        <v>70134.538545760806</v>
-      </c>
-      <c r="G18" s="52">
+        <v>48042.158903846161</v>
+      </c>
+      <c r="G18" s="37">
         <f>+(($T$5*2)/(1-$B$11))</f>
-        <v>80153.758338012354</v>
-      </c>
-      <c r="H18" s="52">
+        <v>54905.324461538468</v>
+      </c>
+      <c r="H18" s="37">
         <f>+(($T$5*2.5)/(1-$B$11))</f>
-        <v>100192.19792251545</v>
-      </c>
-      <c r="I18" s="52">
-        <f t="shared" si="27"/>
-        <v>320615.03335204942</v>
+        <v>68631.655576923091</v>
+      </c>
+      <c r="I18" s="37">
+        <f t="shared" si="28"/>
+        <v>219621.29784615387</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A19" s="51" t="s">
+      <c r="A19" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="52">
+      <c r="B19" s="37">
         <f>+(($T$6*1)/(1-$B$11))</f>
-        <v>38673.173385738351</v>
-      </c>
-      <c r="C19" s="52">
+        <v>26491.123769230773</v>
+      </c>
+      <c r="C19" s="37">
         <f>+(($T$6*0.35)/(1-$B$11))</f>
-        <v>13535.610685008423</v>
-      </c>
-      <c r="D19" s="52">
+        <v>9271.8933192307704</v>
+      </c>
+      <c r="D19" s="37">
         <f>+(($T$6*1.25)/(1-$B$11))</f>
-        <v>48341.466732172943</v>
-      </c>
-      <c r="E19" s="52">
+        <v>33113.904711538467</v>
+      </c>
+      <c r="E19" s="37">
         <f>+(($T$6*1.75)/(1-$B$11))</f>
-        <v>67678.053425042119</v>
-      </c>
-      <c r="F19" s="52">
+        <v>46359.466596153856</v>
+      </c>
+      <c r="F19" s="37">
         <f>+(($T$6*1.75)/(1-$B$11))</f>
-        <v>67678.053425042119</v>
-      </c>
-      <c r="G19" s="52">
+        <v>46359.466596153856</v>
+      </c>
+      <c r="G19" s="37">
         <f>+(($T$6*2)/(1-$B$11))</f>
-        <v>77346.346771476703</v>
-      </c>
-      <c r="H19" s="52">
+        <v>52982.247538461546</v>
+      </c>
+      <c r="H19" s="37">
         <f>+(($T$6*2.5)/(1-$B$11))</f>
-        <v>96682.933464345886</v>
-      </c>
-      <c r="I19" s="52">
-        <f t="shared" si="27"/>
-        <v>309385.38708590681</v>
+        <v>66227.809423076935</v>
+      </c>
+      <c r="I19" s="37">
+        <f t="shared" si="28"/>
+        <v>211928.99015384619</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A20" s="51" t="s">
+      <c r="A20" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="52">
+      <c r="B20" s="37">
         <f>+(($T$7*1)/(1-$B$11))</f>
-        <v>32031.267153284673</v>
-      </c>
-      <c r="C20" s="52">
+        <v>21941.418000000001</v>
+      </c>
+      <c r="C20" s="37">
         <f>+(($T$7*0.35)/(1-$B$11))</f>
-        <v>11210.943503649634</v>
-      </c>
-      <c r="D20" s="52">
+        <v>7679.4962999999998</v>
+      </c>
+      <c r="D20" s="37">
         <f>+(($T$7*1.25)/(1-$B$11))</f>
-        <v>40039.083941605837</v>
-      </c>
-      <c r="E20" s="52">
+        <v>27426.772500000003</v>
+      </c>
+      <c r="E20" s="37">
         <f>+(($T$7*1.75)/(1-$B$11))</f>
-        <v>56054.717518248173</v>
-      </c>
-      <c r="F20" s="52">
+        <v>38397.481500000002</v>
+      </c>
+      <c r="F20" s="37">
         <f>+(($T$7*1.75)/(1-$B$11))</f>
-        <v>56054.717518248173</v>
-      </c>
-      <c r="G20" s="52">
+        <v>38397.481500000002</v>
+      </c>
+      <c r="G20" s="37">
         <f>+(($T$7*2)/(1-$B$11))</f>
-        <v>64062.534306569345</v>
-      </c>
-      <c r="H20" s="52">
+        <v>43882.836000000003</v>
+      </c>
+      <c r="H20" s="37">
         <f>+(($T$7*2.5)/(1-$B$11))</f>
-        <v>80078.167883211674</v>
-      </c>
-      <c r="I20" s="52">
-        <f t="shared" si="27"/>
-        <v>256250.13722627738</v>
+        <v>54853.545000000006</v>
+      </c>
+      <c r="I20" s="37">
+        <f t="shared" si="28"/>
+        <v>175531.34400000001</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A21" s="51" t="s">
+      <c r="A21" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="52">
+      <c r="B21" s="37">
         <f>+(($T$8*1)/(1-$B$11))</f>
-        <v>27152.558562605278</v>
-      </c>
-      <c r="C21" s="52">
+        <v>18599.502615384616</v>
+      </c>
+      <c r="C21" s="37">
         <f>+(($T$8*0.35)/(1-$B$11))</f>
-        <v>9503.3954969118458</v>
-      </c>
-      <c r="D21" s="52">
+        <v>6509.8259153846147</v>
+      </c>
+      <c r="D21" s="37">
         <f>+(($T$8*1.25)/(1-$B$11))</f>
-        <v>33940.698203256594</v>
-      </c>
-      <c r="E21" s="52">
+        <v>23249.378269230769</v>
+      </c>
+      <c r="E21" s="37">
         <f>+(($T$8*1.75)/(1-$B$11))</f>
-        <v>47516.977484559233</v>
-      </c>
-      <c r="F21" s="52">
+        <v>32549.129576923078</v>
+      </c>
+      <c r="F21" s="37">
         <f>+(($T$8*1.75)/(1-$B$11))</f>
-        <v>47516.977484559233</v>
-      </c>
-      <c r="G21" s="52">
+        <v>32549.129576923078</v>
+      </c>
+      <c r="G21" s="37">
         <f>+(($T$8*2)/(1-$B$11))</f>
-        <v>54305.117125210556</v>
-      </c>
-      <c r="H21" s="52">
+        <v>37199.005230769231</v>
+      </c>
+      <c r="H21" s="37">
         <f>+(($T$8*2.5)/(1-$B$11))</f>
-        <v>67881.396406513188</v>
-      </c>
-      <c r="I21" s="52">
-        <f t="shared" si="27"/>
-        <v>217220.46850084222</v>
+        <v>46498.756538461537</v>
+      </c>
+      <c r="I21" s="37">
+        <f t="shared" si="28"/>
+        <v>148796.02092307693</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A22" s="51" t="s">
+      <c r="A22" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="52">
+      <c r="B22" s="37">
         <f>+(($T$9*1)/(1-$B$11))</f>
-        <v>32031.267153284673</v>
-      </c>
-      <c r="C22" s="52">
+        <v>21941.418000000001</v>
+      </c>
+      <c r="C22" s="37">
         <f>+(($T$9*0.35)/(1-$B$11))</f>
-        <v>11210.943503649634</v>
-      </c>
-      <c r="D22" s="52">
+        <v>7679.4962999999998</v>
+      </c>
+      <c r="D22" s="37">
         <f>+(($T$9*1.25)/(1-$B$11))</f>
-        <v>40039.083941605837</v>
-      </c>
-      <c r="E22" s="52">
+        <v>27426.772500000003</v>
+      </c>
+      <c r="E22" s="37">
         <f>+(($T$9*1.75)/(1-$B$11))</f>
-        <v>56054.717518248173</v>
-      </c>
-      <c r="F22" s="52">
+        <v>38397.481500000002</v>
+      </c>
+      <c r="F22" s="37">
         <f>+(($T$9*1.75)/(1-$B$11))</f>
-        <v>56054.717518248173</v>
-      </c>
-      <c r="G22" s="52">
+        <v>38397.481500000002</v>
+      </c>
+      <c r="G22" s="37">
         <f>+(($T$9*2)/(1-$B$11))</f>
-        <v>64062.534306569345</v>
-      </c>
-      <c r="H22" s="52">
+        <v>43882.836000000003</v>
+      </c>
+      <c r="H22" s="37">
         <f>+(($T$9*2.5)/(1-$B$11))</f>
-        <v>80078.167883211674</v>
-      </c>
-      <c r="I22" s="52">
-        <f t="shared" si="27"/>
-        <v>256250.13722627738</v>
+        <v>54853.545000000006</v>
+      </c>
+      <c r="I22" s="37">
+        <f t="shared" si="28"/>
+        <v>175531.34400000001</v>
       </c>
     </row>
   </sheetData>
@@ -2734,799 +2741,799 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="49"/>
-      <c r="B1" s="49" t="s">
+      <c r="A1" s="35"/>
+      <c r="B1" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="49" t="s">
+      <c r="C1" s="35" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="49" t="s">
+      <c r="D1" s="35" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="51" t="str">
+      <c r="A2" s="36" t="str">
         <f>CONCATENATE(B2,C2)</f>
         <v>RESIDENTE DE OBRAHORA ORDINARIA</v>
       </c>
-      <c r="B2" s="51" t="s">
+      <c r="B2" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="59" t="s">
+      <c r="C2" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="52">
+      <c r="D2" s="37">
         <f>VLOOKUP(B2,Tabla!$A$15:$H$22,2,FALSE)</f>
-        <v>38941.98304323414</v>
+        <v>21862.75838461539</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="51" t="str">
+      <c r="A3" s="36" t="str">
         <f t="shared" ref="A3:A50" si="0">CONCATENATE(B3,C3)</f>
         <v>RESIDENTE DE OBRARECARGO NOCTURNO</v>
       </c>
-      <c r="B3" s="51" t="s">
+      <c r="B3" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="59" t="s">
+      <c r="C3" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="D3" s="52">
+      <c r="D3" s="37">
         <f>VLOOKUP(B3,Tabla!$A$15:$H$22,3,FALSE)</f>
-        <v>13629.694065131949</v>
+        <v>7651.9654346153857</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="51" t="str">
+      <c r="A4" s="36" t="str">
         <f t="shared" si="0"/>
         <v>RESIDENTE DE OBRAHORA EXTRA DIURNA</v>
       </c>
-      <c r="B4" s="51" t="s">
+      <c r="B4" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="C4" s="59" t="s">
+      <c r="C4" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="52">
+      <c r="D4" s="37">
         <f>VLOOKUP(B4,Tabla!$A$15:$H$22,4,FALSE)</f>
-        <v>48677.478804042687</v>
+        <v>27328.447980769237</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="51" t="str">
+      <c r="A5" s="36" t="str">
         <f t="shared" si="0"/>
         <v>RESIDENTE DE OBRAHORA EXTRA NOCTURNA</v>
       </c>
-      <c r="B5" s="51" t="s">
+      <c r="B5" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="C5" s="59" t="s">
+      <c r="C5" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="D5" s="52">
+      <c r="D5" s="37">
         <f>VLOOKUP(B5,Tabla!$A$15:$H$22,5,FALSE)</f>
-        <v>68148.470325659757</v>
+        <v>38259.827173076934</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="51" t="str">
+      <c r="A6" s="36" t="str">
         <f t="shared" si="0"/>
         <v>RESIDENTE DE OBRAHORA DOMINICAL</v>
       </c>
-      <c r="B6" s="51" t="s">
+      <c r="B6" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="C6" s="59" t="s">
+      <c r="C6" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="52">
+      <c r="D6" s="37">
         <f>VLOOKUP(B6,Tabla!$A$15:$H$22,6,FALSE)</f>
-        <v>68148.470325659757</v>
+        <v>38259.827173076934</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="51" t="str">
+      <c r="A7" s="36" t="str">
         <f t="shared" si="0"/>
         <v>RESIDENTE DE OBRAHORA EXTRA DOMINICAL (DIURNA)</v>
       </c>
-      <c r="B7" s="51" t="s">
+      <c r="B7" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="C7" s="59" t="s">
+      <c r="C7" s="42" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="52">
+      <c r="D7" s="37">
         <f>VLOOKUP(B7,Tabla!$A$15:$H$22,7,FALSE)</f>
-        <v>77883.966086468281</v>
+        <v>43725.51676923078</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="51" t="str">
+      <c r="A8" s="36" t="str">
         <f t="shared" si="0"/>
         <v>RESIDENTE DE OBRAHORA EXTRA DOMINICAL (NOCTURNA)</v>
       </c>
-      <c r="B8" s="51" t="s">
+      <c r="B8" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="59" t="s">
+      <c r="C8" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="52">
+      <c r="D8" s="37">
         <f>VLOOKUP(B8,Tabla!$A$15:$H$22,8,FALSE)</f>
-        <v>97354.957608085373</v>
+        <v>54656.895961538474</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="51" t="str">
+      <c r="A9" s="36" t="str">
         <f t="shared" si="0"/>
         <v>ING. SUPERVHORA ORDINARIA</v>
       </c>
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="59" t="s">
+      <c r="C9" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="52">
+      <c r="D9" s="37">
         <f>VLOOKUP(B9,Tabla!$A$15:$H$22,2,FALSE)</f>
-        <v>36836.424368332402</v>
+        <v>25232.950692307695</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="51" t="str">
+      <c r="A10" s="36" t="str">
         <f t="shared" si="0"/>
         <v>ING. SUPERVRECARGO NOCTURNO</v>
       </c>
-      <c r="B10" s="51" t="s">
+      <c r="B10" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="59" t="s">
+      <c r="C10" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="52">
+      <c r="D10" s="37">
         <f>VLOOKUP(B10,Tabla!$A$15:$H$22,3,FALSE)</f>
-        <v>12892.748528916338</v>
+        <v>8831.5327423076924</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="51" t="str">
+      <c r="A11" s="36" t="str">
         <f t="shared" si="0"/>
         <v>ING. SUPERVHORA EXTRA DIURNA</v>
       </c>
-      <c r="B11" s="51" t="s">
+      <c r="B11" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="59" t="s">
+      <c r="C11" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="52">
+      <c r="D11" s="37">
         <f>VLOOKUP(B11,Tabla!$A$15:$H$22,4,FALSE)</f>
-        <v>46045.530460415503</v>
+        <v>31541.18836538462</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="51" t="str">
+      <c r="A12" s="36" t="str">
         <f t="shared" si="0"/>
         <v>ING. SUPERVHORA EXTRA NOCTURNA</v>
       </c>
-      <c r="B12" s="51" t="s">
+      <c r="B12" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="59" t="s">
+      <c r="C12" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="52">
+      <c r="D12" s="37">
         <f>VLOOKUP(B12,Tabla!$A$15:$H$22,5,FALSE)</f>
-        <v>64463.742644581696</v>
+        <v>44157.663711538466</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="51" t="str">
+      <c r="A13" s="36" t="str">
         <f t="shared" si="0"/>
         <v>ING. SUPERVHORA DOMINICAL</v>
       </c>
-      <c r="B13" s="51" t="s">
+      <c r="B13" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="59" t="s">
+      <c r="C13" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="52">
+      <c r="D13" s="37">
         <f>VLOOKUP(B13,Tabla!$A$15:$H$22,6,FALSE)</f>
-        <v>64463.742644581696</v>
+        <v>44157.663711538466</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="51" t="str">
+      <c r="A14" s="36" t="str">
         <f t="shared" si="0"/>
         <v>ING. SUPERVHORA EXTRA DOMINICAL (DIURNA)</v>
       </c>
-      <c r="B14" s="51" t="s">
+      <c r="B14" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="59" t="s">
+      <c r="C14" s="42" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="52">
+      <c r="D14" s="37">
         <f>VLOOKUP(B14,Tabla!$A$15:$H$22,7,FALSE)</f>
-        <v>73672.848736664804</v>
+        <v>50465.90138461539</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="51" t="str">
+      <c r="A15" s="36" t="str">
         <f t="shared" si="0"/>
         <v>ING. SUPERVHORA EXTRA DOMINICAL (NOCTURNA)</v>
       </c>
-      <c r="B15" s="51" t="s">
+      <c r="B15" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="59" t="s">
+      <c r="C15" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="D15" s="52">
+      <c r="D15" s="37">
         <f>VLOOKUP(B15,Tabla!$A$15:$H$22,8,FALSE)</f>
-        <v>92091.060920831005</v>
+        <v>63082.37673076924</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="51" t="str">
+      <c r="A16" s="36" t="str">
         <f t="shared" si="0"/>
         <v>SOLDADORHORA ORDINARIA</v>
       </c>
-      <c r="B16" s="51" t="s">
+      <c r="B16" s="36" t="s">
         <v>80</v>
       </c>
-      <c r="C16" s="59" t="s">
+      <c r="C16" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="52">
+      <c r="D16" s="37">
         <f>VLOOKUP(B16,Tabla!$A$15:$H$22,2,FALSE)</f>
-        <v>40076.879169006177</v>
+        <v>27452.662230769234</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="51" t="str">
+      <c r="A17" s="36" t="str">
         <f t="shared" si="0"/>
         <v>SOLDADORRECARGO NOCTURNO</v>
       </c>
-      <c r="B17" s="51" t="s">
+      <c r="B17" s="36" t="s">
         <v>80</v>
       </c>
-      <c r="C17" s="59" t="s">
+      <c r="C17" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="52">
+      <c r="D17" s="37">
         <f>VLOOKUP(B17,Tabla!$A$15:$H$22,3,FALSE)</f>
-        <v>14026.907709152161</v>
+        <v>9608.4317807692314</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="51" t="str">
+      <c r="A18" s="36" t="str">
         <f t="shared" si="0"/>
         <v>SOLDADORHORA EXTRA DIURNA</v>
       </c>
-      <c r="B18" s="51" t="s">
+      <c r="B18" s="36" t="s">
         <v>80</v>
       </c>
-      <c r="C18" s="59" t="s">
+      <c r="C18" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="52">
+      <c r="D18" s="37">
         <f>VLOOKUP(B18,Tabla!$A$15:$H$22,4,FALSE)</f>
-        <v>50096.098961257725</v>
+        <v>34315.827788461545</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="51" t="str">
+      <c r="A19" s="36" t="str">
         <f t="shared" si="0"/>
         <v>SOLDADORHORA EXTRA NOCTURNA</v>
       </c>
-      <c r="B19" s="51" t="s">
+      <c r="B19" s="36" t="s">
         <v>80</v>
       </c>
-      <c r="C19" s="59" t="s">
+      <c r="C19" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="D19" s="52">
+      <c r="D19" s="37">
         <f>VLOOKUP(B19,Tabla!$A$15:$H$22,5,FALSE)</f>
-        <v>70134.538545760806</v>
+        <v>48042.158903846161</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="51" t="str">
+      <c r="A20" s="36" t="str">
         <f t="shared" si="0"/>
         <v>SOLDADORHORA DOMINICAL</v>
       </c>
-      <c r="B20" s="51" t="s">
+      <c r="B20" s="36" t="s">
         <v>80</v>
       </c>
-      <c r="C20" s="59" t="s">
+      <c r="C20" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="D20" s="52">
+      <c r="D20" s="37">
         <f>VLOOKUP(B20,Tabla!$A$15:$H$22,6,FALSE)</f>
-        <v>70134.538545760806</v>
+        <v>48042.158903846161</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="51" t="str">
+      <c r="A21" s="36" t="str">
         <f t="shared" si="0"/>
         <v>SOLDADORHORA EXTRA DOMINICAL (DIURNA)</v>
       </c>
-      <c r="B21" s="51" t="s">
+      <c r="B21" s="36" t="s">
         <v>80</v>
       </c>
-      <c r="C21" s="59" t="s">
+      <c r="C21" s="42" t="s">
         <v>50</v>
       </c>
-      <c r="D21" s="52">
+      <c r="D21" s="37">
         <f>VLOOKUP(B21,Tabla!$A$15:$H$22,7,FALSE)</f>
-        <v>80153.758338012354</v>
+        <v>54905.324461538468</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="51" t="str">
+      <c r="A22" s="36" t="str">
         <f t="shared" si="0"/>
         <v>SOLDADORHORA EXTRA DOMINICAL (NOCTURNA)</v>
       </c>
-      <c r="B22" s="51" t="s">
+      <c r="B22" s="36" t="s">
         <v>80</v>
       </c>
-      <c r="C22" s="59" t="s">
+      <c r="C22" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="52">
+      <c r="D22" s="37">
         <f>VLOOKUP(B22,Tabla!$A$15:$H$22,8,FALSE)</f>
-        <v>100192.19792251545</v>
+        <v>68631.655576923091</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="51" t="str">
+      <c r="A23" s="36" t="str">
         <f t="shared" si="0"/>
         <v>TUBEROHORA ORDINARIA</v>
       </c>
-      <c r="B23" s="51" t="s">
+      <c r="B23" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="59" t="s">
+      <c r="C23" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="D23" s="52">
+      <c r="D23" s="37">
         <f>VLOOKUP(B23,Tabla!$A$15:$H$22,2,FALSE)</f>
-        <v>38673.173385738351</v>
+        <v>26491.123769230773</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="51" t="str">
+      <c r="A24" s="36" t="str">
         <f t="shared" si="0"/>
         <v>TUBERORECARGO NOCTURNO</v>
       </c>
-      <c r="B24" s="51" t="s">
+      <c r="B24" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="C24" s="59" t="s">
+      <c r="C24" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="52">
+      <c r="D24" s="37">
         <f>VLOOKUP(B24,Tabla!$A$15:$H$22,3,FALSE)</f>
-        <v>13535.610685008423</v>
+        <v>9271.8933192307704</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="51" t="str">
+      <c r="A25" s="36" t="str">
         <f t="shared" si="0"/>
         <v>TUBEROHORA EXTRA DIURNA</v>
       </c>
-      <c r="B25" s="51" t="s">
+      <c r="B25" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="C25" s="59" t="s">
+      <c r="C25" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="D25" s="52">
+      <c r="D25" s="37">
         <f>VLOOKUP(B25,Tabla!$A$15:$H$22,4,FALSE)</f>
-        <v>48341.466732172943</v>
+        <v>33113.904711538467</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="51" t="str">
+      <c r="A26" s="36" t="str">
         <f t="shared" si="0"/>
         <v>TUBEROHORA EXTRA NOCTURNA</v>
       </c>
-      <c r="B26" s="51" t="s">
+      <c r="B26" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="C26" s="59" t="s">
+      <c r="C26" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="D26" s="52">
+      <c r="D26" s="37">
         <f>VLOOKUP(B26,Tabla!$A$15:$H$22,5,FALSE)</f>
-        <v>67678.053425042119</v>
+        <v>46359.466596153856</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="51" t="str">
+      <c r="A27" s="36" t="str">
         <f t="shared" si="0"/>
         <v>TUBEROHORA DOMINICAL</v>
       </c>
-      <c r="B27" s="51" t="s">
+      <c r="B27" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="C27" s="59" t="s">
+      <c r="C27" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="D27" s="52">
+      <c r="D27" s="37">
         <f>VLOOKUP(B27,Tabla!$A$15:$H$22,6,FALSE)</f>
-        <v>67678.053425042119</v>
+        <v>46359.466596153856</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="51" t="str">
+      <c r="A28" s="36" t="str">
         <f t="shared" si="0"/>
         <v>TUBEROHORA EXTRA DOMINICAL (DIURNA)</v>
       </c>
-      <c r="B28" s="51" t="s">
+      <c r="B28" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="C28" s="59" t="s">
+      <c r="C28" s="42" t="s">
         <v>50</v>
       </c>
-      <c r="D28" s="52">
+      <c r="D28" s="37">
         <f>VLOOKUP(B28,Tabla!$A$15:$H$22,7,FALSE)</f>
-        <v>77346.346771476703</v>
+        <v>52982.247538461546</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="51" t="str">
+      <c r="A29" s="36" t="str">
         <f t="shared" si="0"/>
         <v>TUBEROHORA EXTRA DOMINICAL (NOCTURNA)</v>
       </c>
-      <c r="B29" s="51" t="s">
+      <c r="B29" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="C29" s="59" t="s">
+      <c r="C29" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="D29" s="52">
+      <c r="D29" s="37">
         <f>VLOOKUP(B29,Tabla!$A$15:$H$22,8,FALSE)</f>
-        <v>96682.933464345886</v>
+        <v>66227.809423076935</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="51" t="str">
+      <c r="A30" s="36" t="str">
         <f t="shared" si="0"/>
         <v>PAILERO MONTADORHORA ORDINARIA</v>
       </c>
-      <c r="B30" s="51" t="s">
+      <c r="B30" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="C30" s="59" t="s">
+      <c r="C30" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="52">
+      <c r="D30" s="37">
         <f>VLOOKUP(B30,Tabla!$A$15:$H$22,2,FALSE)</f>
-        <v>32031.267153284673</v>
+        <v>21941.418000000001</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="51" t="str">
+      <c r="A31" s="36" t="str">
         <f t="shared" si="0"/>
         <v>PAILERO MONTADORRECARGO NOCTURNO</v>
       </c>
-      <c r="B31" s="51" t="s">
+      <c r="B31" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="C31" s="59" t="s">
+      <c r="C31" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="D31" s="52">
+      <c r="D31" s="37">
         <f>VLOOKUP(B31,Tabla!$A$15:$H$22,3,FALSE)</f>
-        <v>11210.943503649634</v>
+        <v>7679.4962999999998</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="51" t="str">
+      <c r="A32" s="36" t="str">
         <f t="shared" si="0"/>
         <v>PAILERO MONTADORHORA EXTRA DIURNA</v>
       </c>
-      <c r="B32" s="51" t="s">
+      <c r="B32" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="C32" s="59" t="s">
+      <c r="C32" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="D32" s="52">
+      <c r="D32" s="37">
         <f>VLOOKUP(B32,Tabla!$A$15:$H$22,4,FALSE)</f>
-        <v>40039.083941605837</v>
+        <v>27426.772500000003</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="51" t="str">
+      <c r="A33" s="36" t="str">
         <f t="shared" si="0"/>
         <v>PAILERO MONTADORHORA EXTRA NOCTURNA</v>
       </c>
-      <c r="B33" s="51" t="s">
+      <c r="B33" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="C33" s="59" t="s">
+      <c r="C33" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="D33" s="52">
+      <c r="D33" s="37">
         <f>VLOOKUP(B33,Tabla!$A$15:$H$22,5,FALSE)</f>
-        <v>56054.717518248173</v>
+        <v>38397.481500000002</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="51" t="str">
+      <c r="A34" s="36" t="str">
         <f t="shared" si="0"/>
         <v>PAILERO MONTADORHORA DOMINICAL</v>
       </c>
-      <c r="B34" s="51" t="s">
+      <c r="B34" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="C34" s="59" t="s">
+      <c r="C34" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="D34" s="52">
+      <c r="D34" s="37">
         <f>VLOOKUP(B34,Tabla!$A$15:$H$22,6,FALSE)</f>
-        <v>56054.717518248173</v>
+        <v>38397.481500000002</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="51" t="str">
+      <c r="A35" s="36" t="str">
         <f t="shared" si="0"/>
         <v>PAILERO MONTADORHORA EXTRA DOMINICAL (DIURNA)</v>
       </c>
-      <c r="B35" s="51" t="s">
+      <c r="B35" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="C35" s="59" t="s">
+      <c r="C35" s="42" t="s">
         <v>50</v>
       </c>
-      <c r="D35" s="52">
+      <c r="D35" s="37">
         <f>VLOOKUP(B35,Tabla!$A$15:$H$22,7,FALSE)</f>
-        <v>64062.534306569345</v>
+        <v>43882.836000000003</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="51" t="str">
+      <c r="A36" s="36" t="str">
         <f t="shared" si="0"/>
         <v>PAILERO MONTADORHORA EXTRA DOMINICAL (NOCTURNA)</v>
       </c>
-      <c r="B36" s="51" t="s">
+      <c r="B36" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="C36" s="59" t="s">
+      <c r="C36" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="D36" s="52">
+      <c r="D36" s="37">
         <f>VLOOKUP(B36,Tabla!$A$15:$H$22,8,FALSE)</f>
-        <v>80078.167883211674</v>
+        <v>54853.545000000006</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="51" t="str">
+      <c r="A37" s="36" t="str">
         <f t="shared" si="0"/>
         <v>AYUDANTEHORA ORDINARIA</v>
       </c>
-      <c r="B37" s="51" t="s">
+      <c r="B37" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="C37" s="59" t="s">
+      <c r="C37" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="D37" s="52">
+      <c r="D37" s="37">
         <f>VLOOKUP(B37,Tabla!$A$15:$H$22,2,FALSE)</f>
-        <v>27152.558562605278</v>
+        <v>18599.502615384616</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="51" t="str">
+      <c r="A38" s="36" t="str">
         <f t="shared" si="0"/>
         <v>AYUDANTERECARGO NOCTURNO</v>
       </c>
-      <c r="B38" s="51" t="s">
+      <c r="B38" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="C38" s="59" t="s">
+      <c r="C38" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="D38" s="52">
+      <c r="D38" s="37">
         <f>VLOOKUP(B38,Tabla!$A$15:$H$22,3,FALSE)</f>
-        <v>9503.3954969118458</v>
+        <v>6509.8259153846147</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="51" t="str">
+      <c r="A39" s="36" t="str">
         <f t="shared" si="0"/>
         <v>AYUDANTEHORA EXTRA DIURNA</v>
       </c>
-      <c r="B39" s="51" t="s">
+      <c r="B39" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="C39" s="59" t="s">
+      <c r="C39" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="D39" s="52">
+      <c r="D39" s="37">
         <f>VLOOKUP(B39,Tabla!$A$15:$H$22,4,FALSE)</f>
-        <v>33940.698203256594</v>
+        <v>23249.378269230769</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="51" t="str">
+      <c r="A40" s="36" t="str">
         <f t="shared" si="0"/>
         <v>AYUDANTEHORA EXTRA NOCTURNA</v>
       </c>
-      <c r="B40" s="51" t="s">
+      <c r="B40" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="C40" s="59" t="s">
+      <c r="C40" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="52">
+      <c r="D40" s="37">
         <f>VLOOKUP(B40,Tabla!$A$15:$H$22,5,FALSE)</f>
-        <v>47516.977484559233</v>
+        <v>32549.129576923078</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="51" t="str">
+      <c r="A41" s="36" t="str">
         <f t="shared" si="0"/>
         <v>AYUDANTEHORA DOMINICAL</v>
       </c>
-      <c r="B41" s="51" t="s">
+      <c r="B41" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="C41" s="59" t="s">
+      <c r="C41" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="52">
+      <c r="D41" s="37">
         <f>VLOOKUP(B41,Tabla!$A$15:$H$22,6,FALSE)</f>
-        <v>47516.977484559233</v>
+        <v>32549.129576923078</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="51" t="str">
+      <c r="A42" s="36" t="str">
         <f t="shared" si="0"/>
         <v>AYUDANTEHORA EXTRA DOMINICAL (DIURNA)</v>
       </c>
-      <c r="B42" s="51" t="s">
+      <c r="B42" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="C42" s="59" t="s">
+      <c r="C42" s="42" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="52">
+      <c r="D42" s="37">
         <f>VLOOKUP(B42,Tabla!$A$15:$H$22,7,FALSE)</f>
-        <v>54305.117125210556</v>
+        <v>37199.005230769231</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="51" t="str">
+      <c r="A43" s="36" t="str">
         <f t="shared" si="0"/>
         <v>AYUDANTEHORA EXTRA DOMINICAL (NOCTURNA)</v>
       </c>
-      <c r="B43" s="51" t="s">
+      <c r="B43" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="C43" s="59" t="s">
+      <c r="C43" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="52">
+      <c r="D43" s="37">
         <f>VLOOKUP(B43,Tabla!$A$15:$H$22,8,FALSE)</f>
-        <v>67881.396406513188</v>
+        <v>46498.756538461537</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="51" t="str">
+      <c r="A44" s="36" t="str">
         <f t="shared" si="0"/>
         <v>SISOHORA ORDINARIA</v>
       </c>
-      <c r="B44" s="51" t="s">
+      <c r="B44" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="C44" s="59" t="s">
+      <c r="C44" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="D44" s="52">
+      <c r="D44" s="37">
         <f>VLOOKUP(B44,Tabla!$A$15:$H$22,2,FALSE)</f>
-        <v>32031.267153284673</v>
+        <v>21941.418000000001</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="51" t="str">
+      <c r="A45" s="36" t="str">
         <f t="shared" si="0"/>
         <v>SISORECARGO NOCTURNO</v>
       </c>
-      <c r="B45" s="51" t="s">
+      <c r="B45" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="C45" s="59" t="s">
+      <c r="C45" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="D45" s="52">
+      <c r="D45" s="37">
         <f>VLOOKUP(B45,Tabla!$A$15:$H$22,3,FALSE)</f>
-        <v>11210.943503649634</v>
+        <v>7679.4962999999998</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="51" t="str">
+      <c r="A46" s="36" t="str">
         <f t="shared" si="0"/>
         <v>SISOHORA EXTRA DIURNA</v>
       </c>
-      <c r="B46" s="51" t="s">
+      <c r="B46" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="C46" s="59" t="s">
+      <c r="C46" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="D46" s="52">
+      <c r="D46" s="37">
         <f>VLOOKUP(B46,Tabla!$A$15:$H$22,4,FALSE)</f>
-        <v>40039.083941605837</v>
+        <v>27426.772500000003</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="51" t="str">
+      <c r="A47" s="36" t="str">
         <f t="shared" si="0"/>
         <v>SISOHORA EXTRA NOCTURNA</v>
       </c>
-      <c r="B47" s="51" t="s">
+      <c r="B47" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="C47" s="59" t="s">
+      <c r="C47" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="D47" s="52">
+      <c r="D47" s="37">
         <f>VLOOKUP(B47,Tabla!$A$15:$H$22,5,FALSE)</f>
-        <v>56054.717518248173</v>
+        <v>38397.481500000002</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="51" t="str">
+      <c r="A48" s="36" t="str">
         <f t="shared" si="0"/>
         <v>SISOHORA DOMINICAL</v>
       </c>
-      <c r="B48" s="51" t="s">
+      <c r="B48" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="C48" s="59" t="s">
+      <c r="C48" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="D48" s="52">
+      <c r="D48" s="37">
         <f>VLOOKUP(B48,Tabla!$A$15:$H$22,6,FALSE)</f>
-        <v>56054.717518248173</v>
+        <v>38397.481500000002</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="51" t="str">
+      <c r="A49" s="36" t="str">
         <f t="shared" si="0"/>
         <v>SISOHORA EXTRA DOMINICAL (DIURNA)</v>
       </c>
-      <c r="B49" s="51" t="s">
+      <c r="B49" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="C49" s="59" t="s">
+      <c r="C49" s="42" t="s">
         <v>50</v>
       </c>
-      <c r="D49" s="52">
+      <c r="D49" s="37">
         <f>VLOOKUP(B49,Tabla!$A$15:$H$22,7,FALSE)</f>
-        <v>64062.534306569345</v>
+        <v>43882.836000000003</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="51" t="str">
+      <c r="A50" s="36" t="str">
         <f t="shared" si="0"/>
         <v>SISOHORA EXTRA DOMINICAL (NOCTURNA)</v>
       </c>
-      <c r="B50" s="51" t="s">
+      <c r="B50" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="C50" s="59" t="s">
+      <c r="C50" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="D50" s="52">
+      <c r="D50" s="37">
         <f>VLOOKUP(B50,Tabla!$A$15:$H$22,8,FALSE)</f>
-        <v>80078.167883211674</v>
+        <v>54853.545000000006</v>
       </c>
     </row>
   </sheetData>
@@ -3539,548 +3546,548 @@
   <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" style="54" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" style="54" customWidth="1"/>
+    <col min="1" max="1" width="4.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" style="3" customWidth="1"/>
     <col min="3" max="3" width="24.7109375" style="5" customWidth="1"/>
-    <col min="4" max="8" width="11.42578125" style="54"/>
+    <col min="4" max="8" width="11.42578125" style="3"/>
     <col min="9" max="9" width="13.140625" style="5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.42578125" style="5"/>
-    <col min="11" max="16384" width="11.42578125" style="54"/>
+    <col min="11" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="60" t="s">
         <v>86</v>
       </c>
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-    </row>
-    <row r="5" spans="1:10" s="53" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="66" t="s">
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="61" t="s">
         <v>63</v>
       </c>
-      <c r="B5" s="66"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-    </row>
-    <row r="6" spans="1:10" s="53" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="67" t="s">
+      <c r="B5" s="61"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="43"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="62" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="67"/>
-      <c r="C6" s="67"/>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="I6" s="60"/>
-      <c r="J6" s="60"/>
-    </row>
-    <row r="7" spans="1:10" s="53" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="67" t="s">
+      <c r="B6" s="62"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="43"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="62" t="s">
         <v>65</v>
       </c>
-      <c r="B7" s="67"/>
-      <c r="C7" s="67"/>
-      <c r="D7" s="67"/>
-      <c r="E7" s="67"/>
-      <c r="F7" s="67"/>
-      <c r="I7" s="60"/>
-      <c r="J7" s="60"/>
-    </row>
-    <row r="8" spans="1:10" s="53" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="68" t="s">
+      <c r="B7" s="62"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="62"/>
+      <c r="E7" s="62"/>
+      <c r="F7" s="62"/>
+      <c r="I7" s="43"/>
+      <c r="J7" s="43"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="63" t="s">
         <v>66</v>
       </c>
-      <c r="B8" s="68"/>
-      <c r="C8" s="68"/>
-      <c r="D8" s="68"/>
-      <c r="E8" s="68"/>
-      <c r="F8" s="68"/>
-      <c r="I8" s="60"/>
-      <c r="J8" s="60"/>
-    </row>
-    <row r="9" spans="1:10" s="53" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="55"/>
-      <c r="C9" s="60"/>
-      <c r="E9" s="79" t="s">
+      <c r="B8" s="63"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="63"/>
+      <c r="F8" s="63"/>
+      <c r="I8" s="43"/>
+      <c r="J8" s="43"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="38"/>
+      <c r="C9" s="43"/>
+      <c r="E9" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="F9" s="80" t="s">
+      <c r="F9" s="55" t="s">
         <v>88</v>
       </c>
-      <c r="I9" s="60"/>
-      <c r="J9" s="60"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="43"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="69" t="s">
+      <c r="A11" s="56" t="s">
         <v>83</v>
       </c>
-      <c r="B11" s="69"/>
-      <c r="C11" s="69"/>
-      <c r="D11" s="69"/>
-      <c r="E11" s="69"/>
-      <c r="F11" s="69"/>
+      <c r="B11" s="56"/>
+      <c r="C11" s="56"/>
+      <c r="D11" s="56"/>
+      <c r="E11" s="56"/>
+      <c r="F11" s="56"/>
     </row>
     <row r="13" spans="1:10" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="75" t="s">
+      <c r="A13" s="58" t="s">
         <v>84</v>
       </c>
-      <c r="B13" s="75"/>
-      <c r="C13" s="75"/>
-      <c r="D13" s="75"/>
-      <c r="E13" s="75"/>
-      <c r="F13" s="75"/>
-      <c r="I13" s="73"/>
-      <c r="J13" s="73"/>
+      <c r="B13" s="58"/>
+      <c r="C13" s="58"/>
+      <c r="D13" s="58"/>
+      <c r="E13" s="58"/>
+      <c r="F13" s="58"/>
+      <c r="I13" s="51"/>
+      <c r="J13" s="51"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="61" t="s">
+      <c r="A15" s="44" t="s">
         <v>76</v>
       </c>
-      <c r="B15" s="61" t="s">
+      <c r="B15" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="61" t="s">
+      <c r="C15" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="D15" s="62" t="s">
+      <c r="D15" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="E15" s="62" t="s">
+      <c r="E15" s="45" t="s">
         <v>70</v>
       </c>
-      <c r="F15" s="62" t="s">
+      <c r="F15" s="45" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="54">
+      <c r="A16" s="3">
         <v>4</v>
       </c>
-      <c r="B16" s="58" t="s">
+      <c r="B16" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="C16" s="72" t="s">
+      <c r="C16" s="50" t="s">
         <v>49</v>
       </c>
       <c r="D16" s="5">
         <f>VLOOKUP(B16&amp;C16,Matriz!$A$1:$D$50,4,FALSE)</f>
-        <v>67678.053425042119</v>
-      </c>
-      <c r="E16" s="64">
+        <v>46359.466596153856</v>
+      </c>
+      <c r="E16" s="47">
         <v>8</v>
       </c>
-      <c r="F16" s="63">
+      <c r="F16" s="46">
         <f>+A16*D16*E16</f>
-        <v>2165697.7096013478</v>
+        <v>1483502.9310769234</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="54">
+      <c r="A17" s="3">
         <v>4</v>
       </c>
-      <c r="B17" s="58" t="s">
+      <c r="B17" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="72" t="s">
+      <c r="C17" s="50" t="s">
         <v>49</v>
       </c>
       <c r="D17" s="5">
         <f>VLOOKUP(B17&amp;C17,Matriz!$A$1:$D$50,4,FALSE)</f>
-        <v>47516.977484559233</v>
-      </c>
-      <c r="E17" s="64">
+        <v>32549.129576923078</v>
+      </c>
+      <c r="E17" s="47">
         <v>8</v>
       </c>
-      <c r="F17" s="63">
+      <c r="F17" s="46">
         <f t="shared" ref="F17:F21" si="0">+A17*D17*E17</f>
-        <v>1520543.2795058955</v>
+        <v>1041572.1464615385</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="54">
+      <c r="A18" s="3">
         <v>1</v>
       </c>
-      <c r="B18" s="58" t="s">
+      <c r="B18" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="72" t="s">
+      <c r="C18" s="50" t="s">
         <v>49</v>
       </c>
       <c r="D18" s="5">
         <f>VLOOKUP(B18&amp;C18,Matriz!$A$1:$D$50,4,FALSE)</f>
-        <v>64463.742644581696</v>
-      </c>
-      <c r="E18" s="64">
+        <v>44157.663711538466</v>
+      </c>
+      <c r="E18" s="47">
         <v>8</v>
       </c>
-      <c r="F18" s="63">
-        <f t="shared" si="0"/>
-        <v>515709.94115665357</v>
+      <c r="F18" s="46">
+        <f t="shared" si="0"/>
+        <v>353261.30969230772</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="54">
+      <c r="A19" s="3">
         <v>1</v>
       </c>
-      <c r="B19" s="58" t="s">
+      <c r="B19" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="C19" s="72" t="s">
+      <c r="C19" s="50" t="s">
         <v>49</v>
       </c>
       <c r="D19" s="5">
         <f>VLOOKUP(B19&amp;C19,Matriz!$A$1:$D$50,4,FALSE)</f>
-        <v>68148.470325659757</v>
-      </c>
-      <c r="E19" s="64">
+        <v>38259.827173076934</v>
+      </c>
+      <c r="E19" s="47">
         <v>8</v>
       </c>
-      <c r="F19" s="63">
-        <f t="shared" si="0"/>
-        <v>545187.76260527805</v>
+      <c r="F19" s="46">
+        <f t="shared" si="0"/>
+        <v>306078.61738461547</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="54">
+      <c r="A20" s="3">
         <v>1</v>
       </c>
-      <c r="B20" s="58" t="s">
+      <c r="B20" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="72" t="s">
+      <c r="C20" s="50" t="s">
         <v>49</v>
       </c>
       <c r="D20" s="5">
         <f>VLOOKUP(B20&amp;C20,Matriz!$A$1:$D$50,4,FALSE)</f>
-        <v>56054.717518248173</v>
-      </c>
-      <c r="E20" s="64">
+        <v>38397.481500000002</v>
+      </c>
+      <c r="E20" s="47">
         <v>8</v>
       </c>
-      <c r="F20" s="63">
-        <f t="shared" si="0"/>
-        <v>448437.74014598539</v>
+      <c r="F20" s="46">
+        <f t="shared" si="0"/>
+        <v>307179.85200000001</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="54">
+      <c r="A21" s="3">
         <v>2</v>
       </c>
-      <c r="B21" s="58" t="s">
+      <c r="B21" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="C21" s="72" t="s">
+      <c r="C21" s="50" t="s">
         <v>49</v>
       </c>
       <c r="D21" s="5">
         <f>VLOOKUP(B21&amp;C21,Matriz!$A$1:$D$50,4,FALSE)</f>
-        <v>56054.717518248173</v>
-      </c>
-      <c r="E21" s="64">
+        <v>38397.481500000002</v>
+      </c>
+      <c r="E21" s="47">
         <v>8</v>
       </c>
-      <c r="F21" s="63">
-        <f t="shared" si="0"/>
-        <v>896875.48029197077</v>
+      <c r="F21" s="46">
+        <f t="shared" si="0"/>
+        <v>614359.70400000003</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="54">
+      <c r="A22" s="3">
         <v>3</v>
       </c>
-      <c r="B22" s="58" t="s">
+      <c r="B22" s="41" t="s">
         <v>80</v>
       </c>
-      <c r="C22" s="72" t="s">
+      <c r="C22" s="50" t="s">
         <v>49</v>
       </c>
       <c r="D22" s="5">
         <f>VLOOKUP(B22&amp;C22,Matriz!$A$1:$D$50,4,FALSE)</f>
-        <v>70134.538545760806</v>
-      </c>
-      <c r="E22" s="64">
+        <v>48042.158903846161</v>
+      </c>
+      <c r="E22" s="47">
         <v>8</v>
       </c>
-      <c r="F22" s="63">
+      <c r="F22" s="46">
         <f>+A22*D22*E22</f>
-        <v>1683228.9250982595</v>
+        <v>1153011.8136923078</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="54">
+      <c r="A23" s="3">
         <v>4</v>
       </c>
-      <c r="B23" s="58" t="s">
+      <c r="B23" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="72" t="s">
+      <c r="C23" s="50" t="s">
         <v>47</v>
       </c>
       <c r="D23" s="5">
         <f>VLOOKUP(B23&amp;C23,Matriz!$A$1:$D$50,4,FALSE)</f>
-        <v>48341.466732172943</v>
-      </c>
-      <c r="E23" s="64">
+        <v>33113.904711538467</v>
+      </c>
+      <c r="E23" s="47">
         <v>3</v>
       </c>
-      <c r="F23" s="63">
+      <c r="F23" s="46">
         <f>+A23*D23*E23</f>
-        <v>580097.60078607535</v>
+        <v>397366.85653846164</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="54">
+      <c r="A24" s="3">
         <v>4</v>
       </c>
-      <c r="B24" s="58" t="s">
+      <c r="B24" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="72" t="s">
+      <c r="C24" s="50" t="s">
         <v>47</v>
       </c>
       <c r="D24" s="5">
         <f>VLOOKUP(B24&amp;C24,Matriz!$A$1:$D$50,4,FALSE)</f>
-        <v>33940.698203256594</v>
-      </c>
-      <c r="E24" s="64">
+        <v>23249.378269230769</v>
+      </c>
+      <c r="E24" s="47">
         <v>3</v>
       </c>
-      <c r="F24" s="63">
+      <c r="F24" s="46">
         <f t="shared" ref="F24:F28" si="1">+A24*D24*E24</f>
-        <v>407288.37843907916</v>
+        <v>278992.53923076921</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="54">
+      <c r="A25" s="3">
         <v>1</v>
       </c>
-      <c r="B25" s="58" t="s">
+      <c r="B25" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="C25" s="72" t="s">
+      <c r="C25" s="50" t="s">
         <v>47</v>
       </c>
       <c r="D25" s="5">
         <f>VLOOKUP(B25&amp;C25,Matriz!$A$1:$D$50,4,FALSE)</f>
-        <v>46045.530460415503</v>
-      </c>
-      <c r="E25" s="64">
+        <v>31541.18836538462</v>
+      </c>
+      <c r="E25" s="47">
         <v>3</v>
       </c>
-      <c r="F25" s="63">
+      <c r="F25" s="46">
         <f t="shared" si="1"/>
-        <v>138136.59138124652</v>
+        <v>94623.565096153863</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="54">
+      <c r="A26" s="3">
         <v>1</v>
       </c>
-      <c r="B26" s="58" t="s">
+      <c r="B26" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="C26" s="72" t="s">
+      <c r="C26" s="50" t="s">
         <v>47</v>
       </c>
       <c r="D26" s="5">
         <f>VLOOKUP(B26&amp;C26,Matriz!$A$1:$D$50,4,FALSE)</f>
-        <v>48677.478804042687</v>
-      </c>
-      <c r="E26" s="64">
+        <v>27328.447980769237</v>
+      </c>
+      <c r="E26" s="47">
         <v>3</v>
       </c>
-      <c r="F26" s="63">
+      <c r="F26" s="46">
         <f t="shared" si="1"/>
-        <v>146032.43641212807</v>
+        <v>81985.343942307707</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="54">
+      <c r="A27" s="3">
         <v>1</v>
       </c>
-      <c r="B27" s="58" t="s">
+      <c r="B27" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="72" t="s">
+      <c r="C27" s="50" t="s">
         <v>47</v>
       </c>
       <c r="D27" s="5">
         <f>VLOOKUP(B27&amp;C27,Matriz!$A$1:$D$50,4,FALSE)</f>
-        <v>40039.083941605837</v>
-      </c>
-      <c r="E27" s="64">
+        <v>27426.772500000003</v>
+      </c>
+      <c r="E27" s="47">
         <v>3</v>
       </c>
-      <c r="F27" s="63">
+      <c r="F27" s="46">
         <f t="shared" si="1"/>
-        <v>120117.2518248175</v>
+        <v>82280.317500000005</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="54">
+      <c r="A28" s="3">
         <v>2</v>
       </c>
-      <c r="B28" s="58" t="s">
+      <c r="B28" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="C28" s="72" t="s">
+      <c r="C28" s="50" t="s">
         <v>47</v>
       </c>
       <c r="D28" s="5">
         <f>VLOOKUP(B28&amp;C28,Matriz!$A$1:$D$50,4,FALSE)</f>
-        <v>40039.083941605837</v>
-      </c>
-      <c r="E28" s="64">
+        <v>27426.772500000003</v>
+      </c>
+      <c r="E28" s="47">
         <v>3</v>
       </c>
-      <c r="F28" s="63">
+      <c r="F28" s="46">
         <f t="shared" si="1"/>
-        <v>240234.50364963501</v>
+        <v>164560.63500000001</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="54">
+      <c r="A29" s="3">
         <v>3</v>
       </c>
-      <c r="B29" s="58" t="s">
+      <c r="B29" s="41" t="s">
         <v>80</v>
       </c>
-      <c r="C29" s="72" t="s">
+      <c r="C29" s="50" t="s">
         <v>47</v>
       </c>
       <c r="D29" s="5">
         <f>VLOOKUP(B29&amp;C29,Matriz!$A$1:$D$50,4,FALSE)</f>
-        <v>50096.098961257725</v>
-      </c>
-      <c r="E29" s="64">
+        <v>34315.827788461545</v>
+      </c>
+      <c r="E29" s="47">
         <v>3</v>
       </c>
-      <c r="F29" s="63">
+      <c r="F29" s="46">
         <f>+A29*D29*E29</f>
-        <v>450864.89065131953</v>
+        <v>308842.45009615389</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B30" s="58"/>
-      <c r="C30" s="72"/>
+      <c r="B30" s="41"/>
+      <c r="C30" s="50"/>
       <c r="D30" s="5"/>
-      <c r="E30" s="64"/>
-      <c r="F30" s="63"/>
+      <c r="E30" s="47"/>
+      <c r="F30" s="46"/>
     </row>
     <row r="31" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E31" s="70" t="s">
+      <c r="E31" s="48" t="s">
         <v>82</v>
       </c>
-      <c r="F31" s="71">
+      <c r="F31" s="49">
         <f>SUM(F16:F29)</f>
-        <v>9858452.4915496893</v>
+        <v>6667618.0817115391</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="69" t="s">
+      <c r="A32" s="56" t="s">
         <v>71</v>
       </c>
-      <c r="B32" s="69"/>
-      <c r="C32" s="69"/>
-      <c r="D32" s="69"/>
-      <c r="E32" s="69"/>
+      <c r="B32" s="56"/>
+      <c r="C32" s="56"/>
+      <c r="D32" s="56"/>
+      <c r="E32" s="56"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="57" t="s">
+      <c r="A33" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="B33" s="54" t="s">
+      <c r="B33" s="3" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="54" t="s">
+      <c r="A34" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B34" s="54" t="s">
+      <c r="B34" s="3" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="54" t="s">
+      <c r="A35" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B35" s="54" t="s">
+      <c r="B35" s="3" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="65" t="s">
+      <c r="A37" s="57" t="s">
         <v>77</v>
       </c>
-      <c r="B37" s="65"/>
-      <c r="C37" s="65"/>
-      <c r="D37" s="65"/>
-      <c r="E37" s="65"/>
-      <c r="F37" s="65"/>
+      <c r="B37" s="57"/>
+      <c r="C37" s="57"/>
+      <c r="D37" s="57"/>
+      <c r="E37" s="57"/>
+      <c r="F37" s="57"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="65" t="s">
+      <c r="A40" s="57" t="s">
         <v>78</v>
       </c>
-      <c r="B40" s="65"/>
-      <c r="C40" s="65"/>
-      <c r="D40" s="65"/>
-      <c r="E40" s="65"/>
-      <c r="F40" s="65"/>
+      <c r="B40" s="57"/>
+      <c r="C40" s="57"/>
+      <c r="D40" s="57"/>
+      <c r="E40" s="57"/>
+      <c r="F40" s="57"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="56" t="s">
+      <c r="A42" s="39" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="56" t="s">
+      <c r="A43" s="39" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="56"/>
+      <c r="A44" s="39"/>
     </row>
     <row r="45" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="76"/>
-      <c r="B45" s="76"/>
-      <c r="C45" s="77"/>
-      <c r="D45" s="76"/>
-      <c r="E45" s="76"/>
+      <c r="A45" s="52"/>
+      <c r="B45" s="52"/>
+      <c r="C45" s="53"/>
+      <c r="D45" s="52"/>
+      <c r="E45" s="52"/>
     </row>
     <row r="46" spans="1:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="78" t="s">
+      <c r="A46" s="59" t="s">
         <v>85</v>
       </c>
-      <c r="B46" s="78"/>
-      <c r="C46" s="78"/>
-      <c r="D46" s="78"/>
-      <c r="E46" s="78"/>
-      <c r="F46" s="78"/>
+      <c r="B46" s="59"/>
+      <c r="C46" s="59"/>
+      <c r="D46" s="59"/>
+      <c r="E46" s="59"/>
+      <c r="F46" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A8:F8"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="A32:E32"/>
     <mergeCell ref="A40:F40"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="A46:F46"/>
     <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A8:F8"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A8" r:id="rId1" xr:uid="{740B3ECC-AF06-42B1-B4CA-D263E8D4B0B7}"/>
